--- a/naver-place-crawler/results_nail/부천_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/부천_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V363"/>
+  <dimension ref="A1:V434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -33849,34 +33849,30 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>핸즈온 디자인</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>gm-engineering@naver.com</t>
-        </is>
-      </c>
+          <t>네일도방긋 부천상동점</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>0507-1351-0295</t>
+          <t>0507-1415-1448</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="inlineStr">
         <is>
-          <t>경기도 부천시 소사구 양지로 205 비121호</t>
+          <t>경기도 부천시 원미구 상동로 79 404호</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hands.on__design</t>
+          <t>http://instagram.com/naildo_banggeut</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -33911,30 +33907,6616 @@
         </is>
       </c>
       <c r="P363" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>87</v>
+      </c>
+      <c r="R363" t="n">
+        <v>188</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>1399849914</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1399849914</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>네일다올</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>fpdlzkwkd@naver.com</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>0507-1313-7221</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 은성로67번길 37 1층 네일다올</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_TUcUxj</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>119</v>
+      </c>
+      <c r="R364" t="n">
+        <v>276</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>1167204000</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1167204000</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>네가꿈꾸는일상 부천원종점</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>everymoneytech@naver.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>032-677-4109</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 소사로 706 2층 네가꿈꾸는일상</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/olivemiin_nail</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>14</v>
+      </c>
+      <c r="R365" t="n">
+        <v>95</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>21139509</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21139509</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>손톱만들기</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>fiat710@naver.com</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>070-7591-2400</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 원종로119번길 87</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q366" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
+      <c r="R366" t="n">
+        <v>3</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>13550943</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13550943</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>네일디에르</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>cindy2120@naver.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>0507-1365-3087</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 조마루로 137 포도마을삼보상가 2층 네일디에르</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_dier</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>9</v>
+      </c>
+      <c r="R367" t="n">
+        <v>169</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>1420326180</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1420326180</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>파브네일</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 288 204호 일부</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/_fabnel_</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>33</v>
+      </c>
+      <c r="R368" t="n">
+        <v>176</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>1835333169</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1835333169</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>디어슈블링네일</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>gyunoia@naver.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>0507-1440-8166</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 91 209,210호 디어슈블링네일</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shu_bling</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P369" t="n">
+        <v>1756</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>15</v>
+      </c>
+      <c r="R369" t="n">
+        <v>1771</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>1526749167</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1526749167</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>그루트네일</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>daldal9776@naver.com</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>0507-1379-7692</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 옥길로 124 3층 321호</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/groot_nail</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P370" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q370" t="n">
         <v>0</v>
       </c>
-      <c r="R363" t="n">
+      <c r="R370" t="n">
+        <v>61</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>1758365342</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1758365342</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>써니네일</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>sunnynails_busan@naver.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>032-673-6966</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 중동로420번길 27</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>2</v>
+      </c>
+      <c r="R371" t="n">
+        <v>13</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>1079131022</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1079131022</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>레푸스 부천역점&amp;탑뷰티클래스</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>hhs3556@naver.com</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>0507-1437-7926</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로 465</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/refuss_bucheon_incheon</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>2738</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>810</v>
+      </c>
+      <c r="R372" t="n">
+        <v>3548</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>13277153</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13277153</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>디스코네일</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>eun_taeng__ing@naver.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>0507-1358-9521</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 석천로177번길 11 203-1호</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/disconail_</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>28</v>
+      </c>
+      <c r="R373" t="n">
+        <v>211</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>1616524282</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1616524282</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>032-341-9412</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 소사로 102</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/somenail_sosa</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>8</v>
+      </c>
+      <c r="R374" t="n">
+        <v>36</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>75798628</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/75798628</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>네일쁨</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>minjiyouuu@naver.com</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>0507-1409-0439</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 신흥로 170 위브더스테이트 5단지 236호</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.bbeum</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>25</v>
+      </c>
+      <c r="R375" t="n">
+        <v>156</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>1475534263</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1475534263</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>하츠네일</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>bambisis@naver.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>0507-1441-3695</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 역곡로482번길 86 1층 하츠네일</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xcxabtxj</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>376</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>10</v>
+      </c>
+      <c r="R376" t="n">
+        <v>386</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>1762550491</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1762550491</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>오넬네일</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 소향로 25 서해프라자 514호</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q377" t="n">
         <v>0</v>
       </c>
-      <c r="S363" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T363" t="inlineStr">
+      <c r="R377" t="n">
+        <v>12</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>1512435118</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1512435118</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>이쁨</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>gracejji@naver.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>0507-1341-3285</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 원종로79번길 55</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ippeum_skin</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>57</v>
+      </c>
+      <c r="R378" t="n">
+        <v>93</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>1746391479</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1746391479</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>네일미</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>ange15321@naver.com</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>0507-1400-3835</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 중동로254번길 28 메트로펠리스3차 205호</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nailmi683</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P379" t="n">
+        <v>204</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>10</v>
+      </c>
+      <c r="R379" t="n">
+        <v>214</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>1442176805</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1442176805</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>채이뷰티</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>0507-1435-6996</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 고리울로28번길 12 1층</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/caiyi_1107/</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P380" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>22</v>
+      </c>
+      <c r="R380" t="n">
+        <v>27</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>2010958932</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2010958932</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>온니네일</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>a5672876@naver.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>0507-1372-8665</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 범안로 227</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/only_nail_0825</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P381" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>4</v>
+      </c>
+      <c r="R381" t="n">
+        <v>34</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>1358118409</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1358118409</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>마발라</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>choi170333@naver.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>032-323-2334</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 석천로177번길 11 1층 117호</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>http://instagram.com/mavala_bucheon</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P382" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>0</v>
+      </c>
+      <c r="R382" t="n">
+        <v>14</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>1193471826</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1193471826</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>네일바르네</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>gustj0066@naver.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>0507-1339-0660</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 91</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.bareune</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P383" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>21</v>
+      </c>
+      <c r="R383" t="n">
+        <v>88</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>1624326985</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1624326985</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>네일클로이</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>eeeeeeeer00@naver.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>0507-1302-1623</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 소사로793번길 9 3동 101호</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.chloe_?igsh=MTBzZDQ3eW15N2N5aA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P384" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>0</v>
+      </c>
+      <c r="R384" t="n">
+        <v>61</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>2036080695</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036080695</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>네일물들다</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>norajo89@naver.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>0507-1343-8183</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 까치로 89 스타리버파크 상가102호 네일물들다</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nailmuldlda</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P385" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>9</v>
+      </c>
+      <c r="R385" t="n">
+        <v>59</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>1723421973</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1723421973</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>벨뷰티</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>yih2124@naver.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>0507-1409-4103</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 양지로 205 3층 307호 일부</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/soVctTyh</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P386" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>0</v>
+      </c>
+      <c r="R386" t="n">
+        <v>0</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>2024215983</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024215983</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>씨오 seao</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>thdus5193@naver.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>0506-779-6295</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 조마루로97번길 34-9 1층</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/s.e.a.o_</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P387" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>18</v>
+      </c>
+      <c r="R387" t="n">
+        <v>25</v>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>1958249895</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1958249895</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>바비네일 부천역지하도상가점</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>baeena95@naver.com</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>032-654-9365</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 심곡본동 563</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P388" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>0</v>
+      </c>
+      <c r="R388" t="n">
+        <v>44</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>36732537</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36732537</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>네일온 부천 상동점</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>nail_on_hy@naver.com</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>0507-1307-6978</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 상이로39번길 8-25 1층</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_on_hy</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P389" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>185</v>
+      </c>
+      <c r="R389" t="n">
+        <v>302</v>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>1878574493</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1878574493</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>꼼꼼네일</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>papa_ma@naver.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>0507-1447-1400</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 역곡로482번길 128 1층1호 꼼꼼네일</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P390" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>0</v>
+      </c>
+      <c r="R390" t="n">
+        <v>5</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>1857455212</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1857455212</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>미미네일</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>minji6394@naver.com</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>0507-1341-6394</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로65번길 45 1층 미미네일</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/minji6394/</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>67</v>
+      </c>
+      <c r="R391" t="n">
+        <v>258</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>1082207152</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1082207152</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>루씨르네일</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>starhn1026@naver.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>0507-1349-0714</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로3번길 48</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_JiexjT</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P392" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>32</v>
+      </c>
+      <c r="R392" t="n">
+        <v>97</v>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>1883923944</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1883923944</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>쿼카네일</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>0507-1495-0643</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 송내대로265번길 67 1층 103호 일부</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/quokkaa_nail</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P393" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>0</v>
+      </c>
+      <c r="R393" t="n">
+        <v>11</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>2064615124</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064615124</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>진네일</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>wlsmlei1@naver.com</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>0507-1476-1723</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 옥산로 12 상가동 205호</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail._.jin_</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P394" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>7</v>
+      </c>
+      <c r="R394" t="n">
+        <v>38</v>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>2087952413</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087952413</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>마카롱 네일살롱</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>xiaohua_1988@naver.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>0507-1360-7057</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로47번길 9 중앙자유시장,제35호</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/xiaohua_1988</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P395" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>114</v>
+      </c>
+      <c r="R395" t="n">
+        <v>116</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>1247045481</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1247045481</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>네일아트재료</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>킹콩네일</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>kingkong_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>0507-1382-2034</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로411번길 20 5층 504호</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xbFuxdn</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>0</v>
+      </c>
+      <c r="R396" t="n">
+        <v>0</v>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>1746361290</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1746361290</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>오늘네일</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>today__nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>0507-1467-0915</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로3번길 48 2층 207호 마라톤마라탕옆 창가라인</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/2day._.nail</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>803</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>121</v>
+      </c>
+      <c r="R397" t="n">
+        <v>924</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>1770211029</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1770211029</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>네일마치</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>0507-1323-3033</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 중동로 19</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nailmarch</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P398" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>67</v>
+      </c>
+      <c r="R398" t="n">
+        <v>232</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>1683017280</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1683017280</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>오늘더예쁜네일</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>0507-1384-8154</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 소사로794번길 36 1층 오늘더예쁜네일</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_brow8154</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P399" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>0</v>
+      </c>
+      <c r="R399" t="n">
+        <v>37</v>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>2013492383</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2013492383</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>참스튜디오네일</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>0507-1388-4194</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로3번길 48 피노키오상가 421호</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_charm_studio</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P400" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>18</v>
+      </c>
+      <c r="R400" t="n">
+        <v>396</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>1309737035</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1309737035</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>예쁜여우네일</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>hundido486@naver.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 수도로55번길 6</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P401" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>0</v>
+      </c>
+      <c r="R401" t="n">
+        <v>88</v>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>336050278</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/336050278</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>베리네일</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>yeonee09@naver.com</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>0507-1431-2317</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로445번길 15 1층 105호-1</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_egWGG</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P402" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>2</v>
+      </c>
+      <c r="R402" t="n">
+        <v>83</v>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>1787773615</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1787773615</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>디뮤즈네일</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>0507-1318-5867</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로77번길 55-25 4층 401-1호</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/d.muse_nail</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P403" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>2</v>
+      </c>
+      <c r="R403" t="n">
+        <v>122</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>2019068456</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2019068456</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>미케이네일</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>miknail@naver.com</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>0507-1385-2587</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로30번길 39 1층</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>http://instagram.com/mik79_love</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P404" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>24</v>
+      </c>
+      <c r="R404" t="n">
+        <v>80</v>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>1886831020</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1886831020</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>블링유네일</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>ohnyoou@naver.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>0507-1367-3818</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 원미로57번길 30</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P405" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>1</v>
+      </c>
+      <c r="R405" t="n">
+        <v>8</v>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>1106320517</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1106320517</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>뷰티갤러리</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>hhh0470@naver.com</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 지봉로33번길 4</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P406" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>0</v>
+      </c>
+      <c r="R406" t="n">
+        <v>13</v>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>37316237</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37316237</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>헤라네일</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>heranaillash@naver.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>0507-1394-9141</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 성오로128번길 40 1층 일부호</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/heranail8081</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P407" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>1</v>
+      </c>
+      <c r="R407" t="n">
+        <v>24</v>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>38427183</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38427183</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>쵸이네일</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>yoonvely_94@naver.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>032-665-6011</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 부천로 1</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P408" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>0</v>
+      </c>
+      <c r="R408" t="n">
+        <v>100</v>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>1983733587</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1983733587</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>루메르</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>mellongi123@naver.com</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로749번길 9</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/rumear_nail</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P409" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>44</v>
+      </c>
+      <c r="R409" t="n">
+        <v>321</v>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>1949763985</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1949763985</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>소신네일</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>0507-1318-9445</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 상동로 79</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/soshin_nail</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P410" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>12</v>
+      </c>
+      <c r="R410" t="n">
+        <v>54</v>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>1868258882</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1868258882</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>신나는오늘네일</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>0507-1307-0473</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 경인로 519 206호 쏠에스테틱 내</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/suwF6yQf</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P411" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>0</v>
+      </c>
+      <c r="R411" t="n">
+        <v>24</v>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>1704099953</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1704099953</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>나즈네일</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>nazenail_@naver.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>0507-1365-6841</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 석천로183번길 43 3층 302호</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nazenail_</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P412" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>7</v>
+      </c>
+      <c r="R412" t="n">
+        <v>145</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>1125111933</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1125111933</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>네일,시</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>swimming0609@naver.com</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>0507-1444-1922</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부흥로 100-1 상가동 1층 104호</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xdMecG</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P413" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>0</v>
+      </c>
+      <c r="R413" t="n">
+        <v>163</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>1768130107</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1768130107</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>퀸네일아트 부천역지하도상가점</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 심곡본동 558</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P414" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>0</v>
+      </c>
+      <c r="R414" t="n">
+        <v>2</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>36732610</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36732610</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>네일뜌</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>jjin5116@naver.com</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>0507-1474-9317</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로517번길 9</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_dduu</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P415" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>77</v>
+      </c>
+      <c r="R415" t="n">
+        <v>198</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>1936545979</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1936545979</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>제인네일 중동점</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>ez_hyun@naver.com</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>0507-1408-8020</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 신흥로 170</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P416" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>4</v>
+      </c>
+      <c r="R416" t="n">
+        <v>25</v>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>38337502</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38337502</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>지나브로우네일</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>karuni@naver.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>0507-1393-3491</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 옥길로 116 2층 211호</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P417" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>3</v>
+      </c>
+      <c r="R417" t="n">
+        <v>55</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>1035697486</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1035697486</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>빛난다 그손</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>alswjdvlel@naver.com</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>032-671-8666</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 원종로29번길 41</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/alswjdvlel</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P418" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>2</v>
+      </c>
+      <c r="R418" t="n">
+        <v>10</v>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>104704744</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/104704744</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>네일퀸스</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>skos0427@naver.com</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>0507-1381-7048</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 고리울로52번길 23 네일퀸스</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P419" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>1</v>
+      </c>
+      <c r="R419" t="n">
+        <v>71</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>1470658671</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1470658671</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>서담네일</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>babotenggu@naver.com</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>032-713-9203</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 수도로206번길 28-26 A동 1층 101호</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_vuvxiG</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P420" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>1</v>
+      </c>
+      <c r="R420" t="n">
+        <v>59</v>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>1730331894</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1730331894</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>아코네일</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>atobbb@naver.com</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>0507-1469-6637</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 86 해피플러스 116호</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/atobbb</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P421" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>14</v>
+      </c>
+      <c r="R421" t="n">
+        <v>274</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>1579039648</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1579039648</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>메리네일</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>0507-1317-8346</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 심곡로10번길 86 1층 102호</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/merry_.nail</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P422" t="n">
+        <v>707</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>147</v>
+      </c>
+      <c r="R422" t="n">
+        <v>854</v>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>1987950636</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1987950636</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>부천네일 헤이즈네일</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>96rkgml@naver.com</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>0507-1462-9799</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 길주로 234 힐스테이트중동 상가3층 3011호</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/heize._.nail</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P423" t="n">
+        <v>624</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>63</v>
+      </c>
+      <c r="R423" t="n">
+        <v>687</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>1976609359</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1976609359</t>
+        </is>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>디그니티 뷰티 네일 부천역점</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>jjieun0602@naver.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로3번길 48 420호</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P424" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>14</v>
+      </c>
+      <c r="R424" t="n">
+        <v>18</v>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>1940638347</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1940638347</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>지니크네일</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>colorforme_lab@naver.com</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로3번길 48 3층 331호</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_XAVyb</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P425" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>2</v>
+      </c>
+      <c r="R425" t="n">
+        <v>36</v>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>1043480492</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1043480492</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>윤네일</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>yungreem04@naver.com</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>0507-1358-0315</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로203번길 54</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yun._.naill</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P426" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>16</v>
+      </c>
+      <c r="R426" t="n">
+        <v>23</v>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>1797763420</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1797763420</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>네일유일리</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>happycom93@naver.com</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로167번길 10</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_yuily/</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P427" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>40</v>
+      </c>
+      <c r="R427" t="n">
+        <v>171</v>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>1766753656</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1766753656</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>팰리스골드네일</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>key4590@naver.com</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>0507-1412-1884</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로 341</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/key4590</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P428" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>2</v>
+      </c>
+      <c r="R428" t="n">
+        <v>14</v>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>895307217</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/895307217</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>J Nail Bar</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>ouojihye@naver.com</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>0507-1443-8384</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 조마루로85번길 27</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/j_nailbar</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P429" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>16</v>
+      </c>
+      <c r="R429" t="n">
+        <v>24</v>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>836831079</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/836831079</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>빛나는,네일</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>abql4365@naver.com</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>0507-1360-4531</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부흥로 133 보람마을 아주아파트 상가 1층 134호</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P430" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>66</v>
+      </c>
+      <c r="R430" t="n">
+        <v>185</v>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>1683358557</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1683358557</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>네일 있어</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>nail_isseo@naver.com</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>0507-1448-2370</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부일로445번길 29 2층 201호</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail_isseo</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P431" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>14</v>
+      </c>
+      <c r="R431" t="n">
+        <v>109</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>1925422417</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1925422417</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>네일썸</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>un6ee@naver.com</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>0507-1409-2454</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>경기도 부천시 원미구 부천로3번길 48 피노키오상가 130호 네일썸</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__some/</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P432" t="n">
+        <v>801</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>40</v>
+      </c>
+      <c r="R432" t="n">
+        <v>841</v>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>1526515772</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1526515772</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>네일 린</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>mkkim100493@naver.com</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>0507-1421-0950</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>경기도 부천시 오정구 역곡로482번길 64 1층</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail__lin__</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr"/>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P433" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>0</v>
+      </c>
+      <c r="R433" t="n">
+        <v>54</v>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>2026594698</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2026594698</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>핸즈온 디자인</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>gm-engineering@naver.com</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>0507-1351-0295</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>경기도 부천시 소사구 양지로 205 비121호</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hands.on__design</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P434" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>0</v>
+      </c>
+      <c r="R434" t="n">
+        <v>0</v>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
         <is>
           <t>1584968752</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="U434" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1584968752</t>
         </is>
       </c>
-      <c r="V363" t="inlineStr">
+      <c r="V434" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
